--- a/output/PRM/reports/PRM_Report_Q12026.xlsx
+++ b/output/PRM/reports/PRM_Report_Q12026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onyx4-my.sharepoint.com/personal/jamie_douglas_edinburghairport_com/Documents/Documents/GitHub/EDI_airport_analytics/output/PRM/reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_658C72D8CAD689385B2F26CACF01B58EBB5E2D3F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F630BED-24C5-47D6-BBF0-B8969EFEB10D}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_913C2B791DD04FC3C236E9526D250AAD0CE937CB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47B606B5-2CE9-42ED-96AA-BA94C66E6EDD}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="20" windowWidth="19180" windowHeight="11260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monthly_PRMs" sheetId="1" r:id="rId1"/>
@@ -43,10 +43,52 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="147">
   <si>
-    <t>Month</t>
+    <t>Adhoc Or Planned</t>
   </si>
   <si>
     <t>Unique Count</t>
+  </si>
+  <si>
+    <t>Total PRM</t>
+  </si>
+  <si>
+    <t>% of PRM Demand</t>
+  </si>
+  <si>
+    <t>Ambulift Users</t>
+  </si>
+  <si>
+    <t>Total Ambulift Users</t>
+  </si>
+  <si>
+    <t>% of Ambulift Users</t>
+  </si>
+  <si>
+    <t>Landside RC Users</t>
+  </si>
+  <si>
+    <t>Total Landside RC Users</t>
+  </si>
+  <si>
+    <t>% of Landside RC Users</t>
+  </si>
+  <si>
+    <t>Airside RC Users</t>
+  </si>
+  <si>
+    <t>Total Airside RC Users</t>
+  </si>
+  <si>
+    <t>% of Airside RC Users</t>
+  </si>
+  <si>
+    <t>Ad-Hoc</t>
+  </si>
+  <si>
+    <t>Planned</t>
+  </si>
+  <si>
+    <t>Month</t>
   </si>
   <si>
     <t>Total Pax</t>
@@ -124,39 +166,6 @@
     <t>SSR Code</t>
   </si>
   <si>
-    <t>Total PRM</t>
-  </si>
-  <si>
-    <t>% of PRM Demand</t>
-  </si>
-  <si>
-    <t>Ambulift Users</t>
-  </si>
-  <si>
-    <t>Total Ambulift Users</t>
-  </si>
-  <si>
-    <t>% of Ambulift Users</t>
-  </si>
-  <si>
-    <t>Landside RC Users</t>
-  </si>
-  <si>
-    <t>Total Landside RC Users</t>
-  </si>
-  <si>
-    <t>% of Landside RC Users</t>
-  </si>
-  <si>
-    <t>Airside RC Users</t>
-  </si>
-  <si>
-    <t>Total Airside RC Users</t>
-  </si>
-  <si>
-    <t>% of Airside RC Users</t>
-  </si>
-  <si>
     <t>BDGP</t>
   </si>
   <si>
@@ -209,15 +218,6 @@
   </si>
   <si>
     <t>WELLCHK</t>
-  </si>
-  <si>
-    <t>Adhoc Or Planned</t>
-  </si>
-  <si>
-    <t>Ad-Hoc</t>
-  </si>
-  <si>
-    <t>Planned</t>
   </si>
   <si>
     <t>Job ID</t>
@@ -660,8 +660,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1007,40 +1007,40 @@
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -1078,7 +1078,7 @@
         <v>2026</v>
       </c>
       <c r="L3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -1116,7 +1116,7 @@
         <v>2026</v>
       </c>
       <c r="L4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -1154,7 +1154,7 @@
         <v>2026</v>
       </c>
       <c r="L5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1166,58 +1166,61 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:P7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="12" max="13" width="8.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="26" x14ac:dyDescent="0.6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="26" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>2026</v>
       </c>
@@ -1240,7 +1243,7 @@
         <v>9.6683158333333331E-3</v>
       </c>
       <c r="H3" s="5">
-        <v>-0.8367</v>
+        <v>-83.670423975173875</v>
       </c>
       <c r="I3" s="5">
         <v>-2.7513402164684262</v>
@@ -1252,12 +1255,14 @@
         <v>481</v>
       </c>
       <c r="L3" s="12">
-        <v>1.7016666666666671</v>
+        <v>1.56</v>
       </c>
       <c r="M3" s="13">
-        <v>1.32</v>
-      </c>
-      <c r="N3" s="14"/>
+        <v>0.89</v>
+      </c>
+      <c r="N3" s="14">
+        <v>0.46333333333333337</v>
+      </c>
       <c r="O3" s="15">
         <v>0.9955666666666666</v>
       </c>
@@ -1268,7 +1273,7 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N4" s="5"/>
     </row>
-    <row r="5" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H5" s="17"/>
       <c r="I5" s="18"/>
       <c r="N5" s="17"/>
@@ -1276,7 +1281,7 @@
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C6" s="7"/>
     </row>
-    <row r="7" spans="1:16" ht="21" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C7" s="19"/>
     </row>
   </sheetData>
@@ -1291,19 +1296,19 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>2026</v>
       </c>
@@ -1311,7 +1316,7 @@
         <v>31625</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -1325,7 +1330,7 @@
         <v>14.16967509025271</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>2024</v>
       </c>
@@ -1339,7 +1344,7 @@
         <v>36.644486692015207</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>2023</v>
       </c>
@@ -1365,48 +1370,48 @@
   <sheetData>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="M2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1445,9 +1450,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>568</v>
@@ -1486,9 +1491,9 @@
         <v>2.616516762060507</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="23" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>365</v>
@@ -1527,9 +1532,9 @@
         <v>0.69501226492232215</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B6">
         <v>3439</v>
@@ -1568,9 +1573,9 @@
         <v>7.0727718724448083</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="23" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B7">
         <v>112</v>
@@ -1609,9 +1614,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="23" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>156</v>
@@ -1650,9 +1655,9 @@
         <v>0.12264922322158631</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="23" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -1691,9 +1696,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="23" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B10">
         <v>2802</v>
@@ -1732,9 +1737,9 @@
         <v>0.32706459525756337</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="23" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B11">
         <v>293</v>
@@ -1773,9 +1778,9 @@
         <v>4.0883074407195422E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="23" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B12">
         <v>3315</v>
@@ -1814,9 +1819,9 @@
         <v>1.062959934587081</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="23" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B13">
         <v>15</v>
@@ -1855,9 +1860,9 @@
         <v>4.0883074407195422E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="23" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <v>9</v>
@@ -1896,9 +1901,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="23" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B15">
         <v>1463</v>
@@ -1937,9 +1942,9 @@
         <v>1.8397383483237939</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="23" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B16">
         <v>14012</v>
@@ -1978,9 +1983,9 @@
         <v>49.059689288634509</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="23" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B17">
         <v>11424</v>
@@ -2019,9 +2024,9 @@
         <v>38.26655764513491</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="23" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B18">
         <v>14</v>
@@ -2060,9 +2065,9 @@
         <v>4.0883074407195422E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="23" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B19">
         <v>48</v>
@@ -2101,9 +2106,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="23" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B20">
         <v>9</v>
@@ -2154,48 +2159,48 @@
   <sheetData>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="M2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>6265</v>
@@ -2236,7 +2241,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>25364</v>
@@ -2302,7 +2307,7 @@
         <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G2" t="s">
         <v>64</v>
@@ -2311,13 +2316,13 @@
         <v>65</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
         <v>66</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2347,7 +2352,7 @@
         <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G2" t="s">
         <v>64</v>
@@ -2356,13 +2361,13 @@
         <v>65</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
         <v>66</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
         <v>67</v>
@@ -2394,7 +2399,7 @@
         <v>72</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
         <v>73</v>
@@ -2403,7 +2408,7 @@
         <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J3" s="2">
         <v>46023</v>
@@ -2434,7 +2439,7 @@
         <v>72</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
         <v>73</v>
@@ -2443,7 +2448,7 @@
         <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J4" s="2">
         <v>46023</v>
@@ -2478,7 +2483,7 @@
         <v>71</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
         <v>74</v>
@@ -2487,7 +2492,7 @@
         <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J5" s="2">
         <v>46024</v>
@@ -2525,7 +2530,7 @@
         <v>72</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
         <v>73</v>
@@ -2534,7 +2539,7 @@
         <v>74</v>
       </c>
       <c r="I6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J6" s="2">
         <v>46023</v>
@@ -2565,7 +2570,7 @@
         <v>72</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
         <v>73</v>
@@ -2574,7 +2579,7 @@
         <v>74</v>
       </c>
       <c r="I7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J7" s="2">
         <v>46023</v>
@@ -2609,7 +2614,7 @@
         <v>71</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
         <v>74</v>
@@ -2618,7 +2623,7 @@
         <v>75</v>
       </c>
       <c r="I8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J8" s="2">
         <v>46024</v>
@@ -2656,7 +2661,7 @@
         <v>72</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s">
         <v>73</v>
@@ -2665,7 +2670,7 @@
         <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J9" s="2">
         <v>46023</v>
@@ -2693,7 +2698,7 @@
         <v>71</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
         <v>76</v>
@@ -2702,7 +2707,7 @@
         <v>77</v>
       </c>
       <c r="I10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J10" s="2">
         <v>46024</v>
@@ -2740,7 +2745,7 @@
         <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
         <v>78</v>
@@ -2749,7 +2754,7 @@
         <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J11" s="2">
         <v>46024</v>
@@ -2777,7 +2782,7 @@
         <v>71</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
         <v>79</v>
@@ -2786,7 +2791,7 @@
         <v>80</v>
       </c>
       <c r="I12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J12" s="2">
         <v>46025</v>
@@ -2821,13 +2826,13 @@
         <v>81</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
         <v>82</v>
       </c>
       <c r="I13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J13" s="2">
         <v>46025</v>
@@ -2855,7 +2860,7 @@
         <v>81</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G14" t="s">
         <v>82</v>
@@ -2864,7 +2869,7 @@
         <v>82</v>
       </c>
       <c r="I14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J14" s="2">
         <v>46026</v>
@@ -2902,7 +2907,7 @@
         <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G15" t="s">
         <v>83</v>
@@ -2911,7 +2916,7 @@
         <v>84</v>
       </c>
       <c r="I15" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J15" s="2">
         <v>46026</v>
@@ -2942,7 +2947,7 @@
         <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s">
         <v>83</v>
@@ -2951,7 +2956,7 @@
         <v>84</v>
       </c>
       <c r="I16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J16" s="2">
         <v>46026</v>
@@ -2986,7 +2991,7 @@
         <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G17" t="s">
         <v>84</v>
@@ -2995,7 +3000,7 @@
         <v>85</v>
       </c>
       <c r="I17" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J17" s="2">
         <v>46027</v>
@@ -3033,7 +3038,7 @@
         <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G18" t="s">
         <v>86</v>
@@ -3042,7 +3047,7 @@
         <v>86</v>
       </c>
       <c r="I18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J18" s="2">
         <v>46026</v>
@@ -3073,7 +3078,7 @@
         <v>72</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G19" t="s">
         <v>86</v>
@@ -3082,7 +3087,7 @@
         <v>86</v>
       </c>
       <c r="I19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J19" s="2">
         <v>46026</v>
@@ -3117,7 +3122,7 @@
         <v>71</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s">
         <v>86</v>
@@ -3126,7 +3131,7 @@
         <v>87</v>
       </c>
       <c r="I20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J20" s="2">
         <v>46027</v>
@@ -3164,7 +3169,7 @@
         <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G21" t="s">
         <v>88</v>
@@ -3173,7 +3178,7 @@
         <v>74</v>
       </c>
       <c r="I21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J21" s="2">
         <v>46027</v>
@@ -3201,7 +3206,7 @@
         <v>71</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G22" t="s">
         <v>74</v>
@@ -3210,7 +3215,7 @@
         <v>89</v>
       </c>
       <c r="I22" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J22" s="2">
         <v>46028</v>
@@ -3248,7 +3253,7 @@
         <v>72</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G23" t="s">
         <v>88</v>
@@ -3257,7 +3262,7 @@
         <v>74</v>
       </c>
       <c r="I23" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J23" s="2">
         <v>46027</v>
@@ -3288,7 +3293,7 @@
         <v>72</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G24" t="s">
         <v>88</v>
@@ -3297,7 +3302,7 @@
         <v>74</v>
       </c>
       <c r="I24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J24" s="2">
         <v>46027</v>
@@ -3332,7 +3337,7 @@
         <v>71</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s">
         <v>74</v>
@@ -3341,7 +3346,7 @@
         <v>85</v>
       </c>
       <c r="I25" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J25" s="2">
         <v>46028</v>
@@ -3379,7 +3384,7 @@
         <v>72</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s">
         <v>76</v>
@@ -3388,7 +3393,7 @@
         <v>84</v>
       </c>
       <c r="I26" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J26" s="2">
         <v>46027</v>
@@ -3416,7 +3421,7 @@
         <v>71</v>
       </c>
       <c r="F27" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s">
         <v>84</v>
@@ -3425,7 +3430,7 @@
         <v>90</v>
       </c>
       <c r="I27" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J27" s="2">
         <v>46028</v>
@@ -3463,7 +3468,7 @@
         <v>72</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G28" t="s">
         <v>76</v>
@@ -3472,7 +3477,7 @@
         <v>91</v>
       </c>
       <c r="I28" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J28" s="2">
         <v>46027</v>
@@ -3503,7 +3508,7 @@
         <v>72</v>
       </c>
       <c r="F29" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G29" t="s">
         <v>76</v>
@@ -3512,7 +3517,7 @@
         <v>91</v>
       </c>
       <c r="I29" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J29" s="2">
         <v>46027</v>
@@ -3547,7 +3552,7 @@
         <v>71</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G30" t="s">
         <v>91</v>
@@ -3556,7 +3561,7 @@
         <v>90</v>
       </c>
       <c r="I30" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J30" s="2">
         <v>46028</v>
@@ -3594,7 +3599,7 @@
         <v>72</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s">
         <v>92</v>
@@ -3603,7 +3608,7 @@
         <v>74</v>
       </c>
       <c r="I31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J31" s="2">
         <v>46027</v>
@@ -3634,7 +3639,7 @@
         <v>72</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G32" t="s">
         <v>92</v>
@@ -3643,7 +3648,7 @@
         <v>74</v>
       </c>
       <c r="I32" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J32" s="2">
         <v>46027</v>
@@ -3678,13 +3683,13 @@
         <v>71</v>
       </c>
       <c r="F33" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G33" t="s">
         <v>74</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J33" s="2">
         <v>46028</v>
@@ -3722,7 +3727,7 @@
         <v>72</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G34" t="s">
         <v>92</v>
@@ -3731,7 +3736,7 @@
         <v>74</v>
       </c>
       <c r="I34" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J34" s="2">
         <v>46027</v>
@@ -3762,7 +3767,7 @@
         <v>72</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G35" t="s">
         <v>92</v>
@@ -3771,7 +3776,7 @@
         <v>74</v>
       </c>
       <c r="I35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J35" s="2">
         <v>46027</v>
@@ -3806,7 +3811,7 @@
         <v>71</v>
       </c>
       <c r="F36" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G36" t="s">
         <v>74</v>
@@ -3815,7 +3820,7 @@
         <v>84</v>
       </c>
       <c r="I36" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J36" s="2">
         <v>46028</v>
@@ -3853,7 +3858,7 @@
         <v>72</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G37" t="s">
         <v>93</v>
@@ -3862,7 +3867,7 @@
         <v>94</v>
       </c>
       <c r="I37" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J37" s="2">
         <v>46027</v>
@@ -3893,7 +3898,7 @@
         <v>72</v>
       </c>
       <c r="F38" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G38" t="s">
         <v>93</v>
@@ -3902,7 +3907,7 @@
         <v>94</v>
       </c>
       <c r="I38" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J38" s="2">
         <v>46027</v>
@@ -3940,7 +3945,7 @@
         <v>72</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G39" t="s">
         <v>94</v>
@@ -3949,7 +3954,7 @@
         <v>95</v>
       </c>
       <c r="I39" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J39" s="2">
         <v>46028</v>
@@ -3987,7 +3992,7 @@
         <v>72</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G40" t="s">
         <v>92</v>
@@ -3996,7 +4001,7 @@
         <v>74</v>
       </c>
       <c r="I40" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J40" s="2">
         <v>46031</v>
@@ -4027,7 +4032,7 @@
         <v>72</v>
       </c>
       <c r="F41" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G41" t="s">
         <v>92</v>
@@ -4036,7 +4041,7 @@
         <v>74</v>
       </c>
       <c r="I41" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J41" s="2">
         <v>46031</v>
@@ -4071,7 +4076,7 @@
         <v>71</v>
       </c>
       <c r="F42" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G42" t="s">
         <v>74</v>
@@ -4080,7 +4085,7 @@
         <v>96</v>
       </c>
       <c r="I42" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J42" s="2">
         <v>46032</v>
@@ -4118,7 +4123,7 @@
         <v>72</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G43" t="s">
         <v>92</v>
@@ -4127,7 +4132,7 @@
         <v>74</v>
       </c>
       <c r="I43" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J43" s="2">
         <v>46031</v>
@@ -4155,7 +4160,7 @@
         <v>71</v>
       </c>
       <c r="F44" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G44" t="s">
         <v>74</v>
@@ -4164,7 +4169,7 @@
         <v>84</v>
       </c>
       <c r="I44" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J44" s="2">
         <v>46032</v>
@@ -4202,7 +4207,7 @@
         <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G45" t="s">
         <v>92</v>
@@ -4211,7 +4216,7 @@
         <v>74</v>
       </c>
       <c r="I45" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J45" s="2">
         <v>46031</v>
@@ -4242,7 +4247,7 @@
         <v>72</v>
       </c>
       <c r="F46" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G46" t="s">
         <v>92</v>
@@ -4251,7 +4256,7 @@
         <v>74</v>
       </c>
       <c r="I46" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J46" s="2">
         <v>46031</v>
@@ -4286,7 +4291,7 @@
         <v>71</v>
       </c>
       <c r="F47" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G47" t="s">
         <v>74</v>
@@ -4295,7 +4300,7 @@
         <v>97</v>
       </c>
       <c r="I47" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J47" s="2">
         <v>46032</v>
@@ -4333,7 +4338,7 @@
         <v>98</v>
       </c>
       <c r="F48" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G48" t="s">
         <v>99</v>
@@ -4342,7 +4347,7 @@
         <v>74</v>
       </c>
       <c r="I48" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J48" s="2">
         <v>46031</v>
@@ -4370,7 +4375,7 @@
         <v>71</v>
       </c>
       <c r="F49" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G49" t="s">
         <v>74</v>
@@ -4379,7 +4384,7 @@
         <v>90</v>
       </c>
       <c r="I49" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J49" s="2">
         <v>46032</v>
@@ -4417,7 +4422,7 @@
         <v>72</v>
       </c>
       <c r="F50" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G50" t="s">
         <v>73</v>
@@ -4426,7 +4431,7 @@
         <v>74</v>
       </c>
       <c r="I50" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J50" s="2">
         <v>46023</v>
@@ -4454,7 +4459,7 @@
         <v>71</v>
       </c>
       <c r="F51" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G51" t="s">
         <v>74</v>
@@ -4463,7 +4468,7 @@
         <v>74</v>
       </c>
       <c r="I51" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J51" s="2">
         <v>46024</v>
@@ -4501,7 +4506,7 @@
         <v>72</v>
       </c>
       <c r="F52" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G52" t="s">
         <v>74</v>
@@ -4510,7 +4515,7 @@
         <v>100</v>
       </c>
       <c r="I52" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J52" s="2">
         <v>46024</v>
@@ -4548,13 +4553,13 @@
         <v>72</v>
       </c>
       <c r="F53" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G53" t="s">
         <v>101</v>
       </c>
       <c r="I53" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J53" s="2">
         <v>46038</v>
@@ -4585,7 +4590,7 @@
         <v>72</v>
       </c>
       <c r="F54" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G54" t="s">
         <v>101</v>
@@ -4594,7 +4599,7 @@
         <v>101</v>
       </c>
       <c r="I54" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J54" s="2">
         <v>46039</v>
@@ -4632,7 +4637,7 @@
         <v>72</v>
       </c>
       <c r="F55" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G55" t="s">
         <v>101</v>
@@ -4641,7 +4646,7 @@
         <v>101</v>
       </c>
       <c r="I55" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J55" s="2">
         <v>46039</v>
@@ -4679,7 +4684,7 @@
         <v>72</v>
       </c>
       <c r="F56" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G56" t="s">
         <v>102</v>
@@ -4688,7 +4693,7 @@
         <v>74</v>
       </c>
       <c r="I56" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J56" s="2">
         <v>46030</v>
@@ -4719,7 +4724,7 @@
         <v>72</v>
       </c>
       <c r="F57" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G57" t="s">
         <v>102</v>
@@ -4728,7 +4733,7 @@
         <v>74</v>
       </c>
       <c r="I57" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J57" s="2">
         <v>46030</v>
@@ -4763,7 +4768,7 @@
         <v>71</v>
       </c>
       <c r="F58" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G58" t="s">
         <v>74</v>
@@ -4772,7 +4777,7 @@
         <v>90</v>
       </c>
       <c r="I58" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J58" s="2">
         <v>46031</v>
@@ -4810,7 +4815,7 @@
         <v>72</v>
       </c>
       <c r="F59" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G59" t="s">
         <v>92</v>
@@ -4819,7 +4824,7 @@
         <v>74</v>
       </c>
       <c r="I59" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J59" s="2">
         <v>46027</v>
@@ -4850,7 +4855,7 @@
         <v>72</v>
       </c>
       <c r="F60" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G60" t="s">
         <v>92</v>
@@ -4859,7 +4864,7 @@
         <v>74</v>
       </c>
       <c r="I60" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J60" s="2">
         <v>46027</v>
@@ -4894,7 +4899,7 @@
         <v>71</v>
       </c>
       <c r="F61" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G61" t="s">
         <v>74</v>
@@ -4903,7 +4908,7 @@
         <v>96</v>
       </c>
       <c r="I61" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J61" s="2">
         <v>46028</v>
@@ -4938,7 +4943,7 @@
         <v>71</v>
       </c>
       <c r="F62" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G62" t="s">
         <v>74</v>
@@ -4947,7 +4952,7 @@
         <v>74</v>
       </c>
       <c r="I62" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J62" s="2">
         <v>46043</v>
@@ -4978,7 +4983,7 @@
         <v>72</v>
       </c>
       <c r="F63" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G63" t="s">
         <v>76</v>
@@ -4987,7 +4992,7 @@
         <v>74</v>
       </c>
       <c r="I63" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J63" s="2">
         <v>46043</v>
@@ -5022,13 +5027,13 @@
         <v>71</v>
       </c>
       <c r="F64" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G64" t="s">
         <v>74</v>
       </c>
       <c r="I64" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J64" s="2">
         <v>46044</v>
@@ -5063,7 +5068,7 @@
         <v>71</v>
       </c>
       <c r="F65" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G65" t="s">
         <v>103</v>
@@ -5072,7 +5077,7 @@
         <v>74</v>
       </c>
       <c r="I65" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J65" s="2">
         <v>46043</v>
@@ -5103,7 +5108,7 @@
         <v>72</v>
       </c>
       <c r="F66" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G66" t="s">
         <v>76</v>
@@ -5112,7 +5117,7 @@
         <v>103</v>
       </c>
       <c r="I66" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J66" s="2">
         <v>46043</v>
@@ -5150,7 +5155,7 @@
         <v>72</v>
       </c>
       <c r="F67" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G67" t="s">
         <v>76</v>
@@ -5159,7 +5164,7 @@
         <v>103</v>
       </c>
       <c r="I67" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J67" s="2">
         <v>46043</v>
@@ -5194,7 +5199,7 @@
         <v>71</v>
       </c>
       <c r="F68" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G68" t="s">
         <v>74</v>
@@ -5203,7 +5208,7 @@
         <v>84</v>
       </c>
       <c r="I68" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J68" s="2">
         <v>46044</v>
@@ -5238,7 +5243,7 @@
         <v>71</v>
       </c>
       <c r="F69" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G69" t="s">
         <v>84</v>
@@ -5247,7 +5252,7 @@
         <v>104</v>
       </c>
       <c r="I69" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J69" s="2">
         <v>46044</v>
@@ -5282,7 +5287,7 @@
         <v>71</v>
       </c>
       <c r="F70" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G70" t="s">
         <v>74</v>
@@ -5291,7 +5296,7 @@
         <v>74</v>
       </c>
       <c r="I70" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J70" s="2">
         <v>46043</v>
@@ -5322,7 +5327,7 @@
         <v>72</v>
       </c>
       <c r="F71" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G71" t="s">
         <v>76</v>
@@ -5331,7 +5336,7 @@
         <v>74</v>
       </c>
       <c r="I71" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J71" s="2">
         <v>46043</v>
@@ -5366,7 +5371,7 @@
         <v>71</v>
       </c>
       <c r="F72" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G72" t="s">
         <v>74</v>
@@ -5375,7 +5380,7 @@
         <v>84</v>
       </c>
       <c r="I72" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J72" s="2">
         <v>46044</v>
@@ -5410,7 +5415,7 @@
         <v>71</v>
       </c>
       <c r="F73" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G73" t="s">
         <v>84</v>
@@ -5419,7 +5424,7 @@
         <v>104</v>
       </c>
       <c r="I73" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J73" s="2">
         <v>46044</v>
@@ -5457,7 +5462,7 @@
         <v>98</v>
       </c>
       <c r="F74" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G74" t="s">
         <v>99</v>
@@ -5466,7 +5471,7 @@
         <v>84</v>
       </c>
       <c r="I74" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J74" s="2">
         <v>46031</v>
@@ -5494,7 +5499,7 @@
         <v>71</v>
       </c>
       <c r="F75" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G75" t="s">
         <v>84</v>
@@ -5503,7 +5508,7 @@
         <v>96</v>
       </c>
       <c r="I75" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J75" s="2">
         <v>46032</v>
@@ -5538,7 +5543,7 @@
         <v>71</v>
       </c>
       <c r="F76" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G76" t="s">
         <v>74</v>
@@ -5547,7 +5552,7 @@
         <v>74</v>
       </c>
       <c r="I76" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J76" s="2">
         <v>46043</v>
@@ -5578,7 +5583,7 @@
         <v>72</v>
       </c>
       <c r="F77" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G77" t="s">
         <v>76</v>
@@ -5587,7 +5592,7 @@
         <v>74</v>
       </c>
       <c r="I77" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J77" s="2">
         <v>46043</v>
@@ -5625,7 +5630,7 @@
         <v>72</v>
       </c>
       <c r="F78" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G78" t="s">
         <v>76</v>
@@ -5634,7 +5639,7 @@
         <v>74</v>
       </c>
       <c r="I78" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J78" s="2">
         <v>46043</v>
@@ -5669,7 +5674,7 @@
         <v>71</v>
       </c>
       <c r="F79" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G79" t="s">
         <v>74</v>
@@ -5678,7 +5683,7 @@
         <v>104</v>
       </c>
       <c r="I79" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J79" s="2">
         <v>46044</v>
@@ -5716,7 +5721,7 @@
         <v>72</v>
       </c>
       <c r="F80" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G80" t="s">
         <v>86</v>
@@ -5725,7 +5730,7 @@
         <v>74</v>
       </c>
       <c r="I80" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J80" s="2">
         <v>46058</v>
@@ -5756,7 +5761,7 @@
         <v>72</v>
       </c>
       <c r="F81" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G81" t="s">
         <v>86</v>
@@ -5765,7 +5770,7 @@
         <v>74</v>
       </c>
       <c r="I81" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J81" s="2">
         <v>46058</v>
@@ -5800,7 +5805,7 @@
         <v>71</v>
       </c>
       <c r="F82" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G82" t="s">
         <v>74</v>
@@ -5809,7 +5814,7 @@
         <v>105</v>
       </c>
       <c r="I82" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J82" s="2">
         <v>46059</v>
@@ -5847,7 +5852,7 @@
         <v>72</v>
       </c>
       <c r="F83" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G83" t="s">
         <v>86</v>
@@ -5856,7 +5861,7 @@
         <v>74</v>
       </c>
       <c r="I83" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J83" s="2">
         <v>46058</v>
@@ -5887,7 +5892,7 @@
         <v>72</v>
       </c>
       <c r="F84" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G84" t="s">
         <v>86</v>
@@ -5896,7 +5901,7 @@
         <v>74</v>
       </c>
       <c r="I84" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J84" s="2">
         <v>46058</v>
@@ -5931,7 +5936,7 @@
         <v>71</v>
       </c>
       <c r="F85" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G85" t="s">
         <v>74</v>
@@ -5940,7 +5945,7 @@
         <v>106</v>
       </c>
       <c r="I85" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J85" s="2">
         <v>46059</v>
@@ -5978,7 +5983,7 @@
         <v>72</v>
       </c>
       <c r="F86" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G86" t="s">
         <v>92</v>
@@ -5987,7 +5992,7 @@
         <v>74</v>
       </c>
       <c r="I86" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J86" s="2">
         <v>46059</v>
@@ -6018,7 +6023,7 @@
         <v>72</v>
       </c>
       <c r="F87" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G87" t="s">
         <v>92</v>
@@ -6027,7 +6032,7 @@
         <v>74</v>
       </c>
       <c r="I87" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J87" s="2">
         <v>46059</v>
@@ -6062,7 +6067,7 @@
         <v>71</v>
       </c>
       <c r="F88" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G88" t="s">
         <v>74</v>
@@ -6071,7 +6076,7 @@
         <v>107</v>
       </c>
       <c r="I88" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J88" s="2">
         <v>46060</v>
@@ -6109,7 +6114,7 @@
         <v>72</v>
       </c>
       <c r="F89" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G89" t="s">
         <v>92</v>
@@ -6118,7 +6123,7 @@
         <v>74</v>
       </c>
       <c r="I89" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J89" s="2">
         <v>46059</v>
@@ -6146,7 +6151,7 @@
         <v>71</v>
       </c>
       <c r="F90" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G90" t="s">
         <v>74</v>
@@ -6155,7 +6160,7 @@
         <v>107</v>
       </c>
       <c r="I90" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J90" s="2">
         <v>46060</v>
@@ -6193,7 +6198,7 @@
         <v>72</v>
       </c>
       <c r="F91" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G91" t="s">
         <v>108</v>
@@ -6202,7 +6207,7 @@
         <v>74</v>
       </c>
       <c r="I91" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J91" s="2">
         <v>46065</v>
@@ -6233,7 +6238,7 @@
         <v>72</v>
       </c>
       <c r="F92" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G92" t="s">
         <v>108</v>
@@ -6242,7 +6247,7 @@
         <v>74</v>
       </c>
       <c r="I92" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J92" s="2">
         <v>46065</v>
@@ -6277,7 +6282,7 @@
         <v>71</v>
       </c>
       <c r="F93" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G93" t="s">
         <v>74</v>
@@ -6286,7 +6291,7 @@
         <v>89</v>
       </c>
       <c r="I93" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J93" s="2">
         <v>46066</v>
@@ -6324,7 +6329,7 @@
         <v>72</v>
       </c>
       <c r="F94" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G94" t="s">
         <v>74</v>
@@ -6333,7 +6338,7 @@
         <v>74</v>
       </c>
       <c r="I94" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J94" s="2">
         <v>46066</v>
@@ -6361,7 +6366,7 @@
         <v>71</v>
       </c>
       <c r="F95" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G95" t="s">
         <v>74</v>
@@ -6370,7 +6375,7 @@
         <v>100</v>
       </c>
       <c r="I95" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J95" s="2">
         <v>46067</v>
@@ -6408,7 +6413,7 @@
         <v>72</v>
       </c>
       <c r="F96" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G96" t="s">
         <v>102</v>
@@ -6417,7 +6422,7 @@
         <v>103</v>
       </c>
       <c r="I96" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J96" s="2">
         <v>46068</v>
@@ -6445,7 +6450,7 @@
         <v>71</v>
       </c>
       <c r="F97" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G97" t="s">
         <v>103</v>
@@ -6454,7 +6459,7 @@
         <v>77</v>
       </c>
       <c r="I97" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J97" s="2">
         <v>46069</v>
@@ -6492,7 +6497,7 @@
         <v>72</v>
       </c>
       <c r="F98" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G98" t="s">
         <v>109</v>
@@ -6501,7 +6506,7 @@
         <v>103</v>
       </c>
       <c r="I98" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J98" s="2">
         <v>46069</v>
@@ -6532,7 +6537,7 @@
         <v>72</v>
       </c>
       <c r="F99" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G99" t="s">
         <v>109</v>
@@ -6541,7 +6546,7 @@
         <v>103</v>
       </c>
       <c r="I99" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J99" s="2">
         <v>46069</v>
@@ -6576,7 +6581,7 @@
         <v>71</v>
       </c>
       <c r="F100" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G100" t="s">
         <v>103</v>
@@ -6585,7 +6590,7 @@
         <v>110</v>
       </c>
       <c r="I100" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J100" s="2">
         <v>46070</v>
@@ -6623,7 +6628,7 @@
         <v>72</v>
       </c>
       <c r="F101" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G101" t="s">
         <v>109</v>
@@ -6632,7 +6637,7 @@
         <v>109</v>
       </c>
       <c r="I101" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J101" s="2">
         <v>46069</v>
@@ -6660,7 +6665,7 @@
         <v>71</v>
       </c>
       <c r="F102" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G102" t="s">
         <v>109</v>
@@ -6669,7 +6674,7 @@
         <v>111</v>
       </c>
       <c r="I102" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J102" s="2">
         <v>46070</v>
@@ -6707,7 +6712,7 @@
         <v>72</v>
       </c>
       <c r="F103" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G103" t="s">
         <v>109</v>
@@ -6716,7 +6721,7 @@
         <v>109</v>
       </c>
       <c r="I103" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J103" s="2">
         <v>46069</v>
@@ -6747,7 +6752,7 @@
         <v>72</v>
       </c>
       <c r="F104" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G104" t="s">
         <v>109</v>
@@ -6756,7 +6761,7 @@
         <v>109</v>
       </c>
       <c r="I104" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J104" s="2">
         <v>46069</v>
@@ -6791,7 +6796,7 @@
         <v>71</v>
       </c>
       <c r="F105" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G105" t="s">
         <v>109</v>
@@ -6800,7 +6805,7 @@
         <v>77</v>
       </c>
       <c r="I105" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J105" s="2">
         <v>46070</v>
@@ -6835,7 +6840,7 @@
         <v>71</v>
       </c>
       <c r="F106" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G106" t="s">
         <v>77</v>
@@ -6844,7 +6849,7 @@
         <v>112</v>
       </c>
       <c r="I106" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J106" s="2">
         <v>46070</v>
@@ -6882,7 +6887,7 @@
         <v>72</v>
       </c>
       <c r="F107" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G107" t="s">
         <v>113</v>
@@ -6891,7 +6896,7 @@
         <v>86</v>
       </c>
       <c r="I107" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J107" s="2">
         <v>46060</v>
@@ -6919,7 +6924,7 @@
         <v>71</v>
       </c>
       <c r="F108" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G108" t="s">
         <v>86</v>
@@ -6928,7 +6933,7 @@
         <v>114</v>
       </c>
       <c r="I108" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J108" s="2">
         <v>46061</v>
@@ -6966,7 +6971,7 @@
         <v>72</v>
       </c>
       <c r="F109" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G109" t="s">
         <v>113</v>
@@ -6975,7 +6980,7 @@
         <v>115</v>
       </c>
       <c r="I109" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J109" s="2">
         <v>46060</v>
@@ -7003,7 +7008,7 @@
         <v>71</v>
       </c>
       <c r="F110" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G110" t="s">
         <v>115</v>
@@ -7012,7 +7017,7 @@
         <v>116</v>
       </c>
       <c r="I110" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J110" s="2">
         <v>46061</v>
@@ -7050,7 +7055,7 @@
         <v>72</v>
       </c>
       <c r="F111" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G111" t="s">
         <v>92</v>
@@ -7059,7 +7064,7 @@
         <v>84</v>
       </c>
       <c r="I111" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J111" s="2">
         <v>46059</v>
@@ -7090,7 +7095,7 @@
         <v>72</v>
       </c>
       <c r="F112" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G112" t="s">
         <v>92</v>
@@ -7099,7 +7104,7 @@
         <v>84</v>
       </c>
       <c r="I112" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J112" s="2">
         <v>46059</v>
@@ -7134,7 +7139,7 @@
         <v>71</v>
       </c>
       <c r="F113" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G113" t="s">
         <v>84</v>
@@ -7143,7 +7148,7 @@
         <v>77</v>
       </c>
       <c r="I113" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J113" s="2">
         <v>46060</v>
@@ -7181,7 +7186,7 @@
         <v>72</v>
       </c>
       <c r="F114" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G114" t="s">
         <v>109</v>
@@ -7190,7 +7195,7 @@
         <v>109</v>
       </c>
       <c r="I114" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J114" s="2">
         <v>46074</v>
@@ -7221,7 +7226,7 @@
         <v>72</v>
       </c>
       <c r="F115" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G115" t="s">
         <v>109</v>
@@ -7230,7 +7235,7 @@
         <v>109</v>
       </c>
       <c r="I115" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J115" s="2">
         <v>46074</v>
@@ -7265,7 +7270,7 @@
         <v>71</v>
       </c>
       <c r="F116" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G116" t="s">
         <v>109</v>
@@ -7274,7 +7279,7 @@
         <v>90</v>
       </c>
       <c r="I116" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J116" s="2">
         <v>46075</v>
@@ -7312,7 +7317,7 @@
         <v>72</v>
       </c>
       <c r="F117" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G117" t="s">
         <v>117</v>
@@ -7321,7 +7326,7 @@
         <v>84</v>
       </c>
       <c r="I117" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J117" s="2">
         <v>46075</v>
@@ -7349,7 +7354,7 @@
         <v>71</v>
       </c>
       <c r="F118" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G118" t="s">
         <v>84</v>
@@ -7358,7 +7363,7 @@
         <v>114</v>
       </c>
       <c r="I118" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J118" s="2">
         <v>46076</v>
@@ -7396,7 +7401,7 @@
         <v>98</v>
       </c>
       <c r="F119" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G119" t="s">
         <v>117</v>
@@ -7405,7 +7410,7 @@
         <v>84</v>
       </c>
       <c r="I119" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J119" s="2">
         <v>46075</v>
@@ -7436,7 +7441,7 @@
         <v>98</v>
       </c>
       <c r="F120" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G120" t="s">
         <v>117</v>
@@ -7445,7 +7450,7 @@
         <v>84</v>
       </c>
       <c r="I120" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J120" s="2">
         <v>46075</v>
@@ -7480,13 +7485,13 @@
         <v>71</v>
       </c>
       <c r="F121" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G121" t="s">
         <v>84</v>
       </c>
       <c r="I121" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J121" s="2">
         <v>46076</v>
@@ -7524,7 +7529,7 @@
         <v>72</v>
       </c>
       <c r="F122" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G122" t="s">
         <v>109</v>
@@ -7533,7 +7538,7 @@
         <v>109</v>
       </c>
       <c r="I122" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J122" s="2">
         <v>46069</v>
@@ -7561,7 +7566,7 @@
         <v>71</v>
       </c>
       <c r="F123" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G123" t="s">
         <v>109</v>
@@ -7570,7 +7575,7 @@
         <v>77</v>
       </c>
       <c r="I123" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J123" s="2">
         <v>46070</v>
@@ -7608,7 +7613,7 @@
         <v>72</v>
       </c>
       <c r="F124" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G124" t="s">
         <v>109</v>
@@ -7617,7 +7622,7 @@
         <v>109</v>
       </c>
       <c r="I124" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J124" s="2">
         <v>46069</v>
@@ -7645,7 +7650,7 @@
         <v>71</v>
       </c>
       <c r="F125" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G125" t="s">
         <v>110</v>
@@ -7654,7 +7659,7 @@
         <v>107</v>
       </c>
       <c r="I125" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J125" s="2">
         <v>46070</v>
@@ -7689,7 +7694,7 @@
         <v>71</v>
       </c>
       <c r="F126" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G126" t="s">
         <v>109</v>
@@ -7698,7 +7703,7 @@
         <v>110</v>
       </c>
       <c r="I126" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J126" s="2">
         <v>46070</v>
@@ -7736,7 +7741,7 @@
         <v>72</v>
       </c>
       <c r="F127" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G127" t="s">
         <v>108</v>
@@ -7745,7 +7750,7 @@
         <v>74</v>
       </c>
       <c r="I127" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J127" s="2">
         <v>46065</v>
@@ -7773,7 +7778,7 @@
         <v>71</v>
       </c>
       <c r="F128" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G128" t="s">
         <v>74</v>
@@ -7782,7 +7787,7 @@
         <v>89</v>
       </c>
       <c r="I128" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J128" s="2">
         <v>46066</v>
@@ -7820,7 +7825,7 @@
         <v>72</v>
       </c>
       <c r="F129" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G129" t="s">
         <v>113</v>
@@ -7829,7 +7834,7 @@
         <v>84</v>
       </c>
       <c r="I129" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J129" s="2">
         <v>46067</v>
@@ -7857,7 +7862,7 @@
         <v>71</v>
       </c>
       <c r="F130" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G130" t="s">
         <v>84</v>
@@ -7866,7 +7871,7 @@
         <v>100</v>
       </c>
       <c r="I130" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J130" s="2">
         <v>46068</v>
@@ -7904,7 +7909,7 @@
         <v>72</v>
       </c>
       <c r="F131" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G131" t="s">
         <v>113</v>
@@ -7913,7 +7918,7 @@
         <v>84</v>
       </c>
       <c r="I131" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J131" s="2">
         <v>46067</v>
@@ -7941,13 +7946,13 @@
         <v>71</v>
       </c>
       <c r="F132" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G132" t="s">
         <v>84</v>
       </c>
       <c r="I132" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J132" s="2">
         <v>46068</v>
@@ -7985,7 +7990,7 @@
         <v>72</v>
       </c>
       <c r="F133" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G133" t="s">
         <v>113</v>
@@ -7994,7 +7999,7 @@
         <v>74</v>
       </c>
       <c r="I133" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J133" s="2">
         <v>46067</v>
@@ -8022,7 +8027,7 @@
         <v>71</v>
       </c>
       <c r="F134" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G134" t="s">
         <v>74</v>
@@ -8031,7 +8036,7 @@
         <v>100</v>
       </c>
       <c r="I134" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J134" s="2">
         <v>46068</v>
@@ -8069,7 +8074,7 @@
         <v>72</v>
       </c>
       <c r="F135" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G135" t="s">
         <v>113</v>
@@ -8078,7 +8083,7 @@
         <v>74</v>
       </c>
       <c r="I135" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J135" s="2">
         <v>46067</v>
@@ -8106,7 +8111,7 @@
         <v>71</v>
       </c>
       <c r="F136" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G136" t="s">
         <v>74</v>
@@ -8115,7 +8120,7 @@
         <v>90</v>
       </c>
       <c r="I136" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J136" s="2">
         <v>46068</v>
@@ -8153,7 +8158,7 @@
         <v>72</v>
       </c>
       <c r="F137" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G137" t="s">
         <v>88</v>
@@ -8162,7 +8167,7 @@
         <v>75</v>
       </c>
       <c r="I137" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J137" s="2">
         <v>46080</v>
@@ -8193,7 +8198,7 @@
         <v>72</v>
       </c>
       <c r="F138" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G138" t="s">
         <v>88</v>
@@ -8202,7 +8207,7 @@
         <v>75</v>
       </c>
       <c r="I138" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J138" s="2">
         <v>46080</v>
@@ -8237,7 +8242,7 @@
         <v>71</v>
       </c>
       <c r="F139" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G139" t="s">
         <v>75</v>
@@ -8246,7 +8251,7 @@
         <v>107</v>
       </c>
       <c r="I139" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J139" s="2">
         <v>46081</v>
@@ -8284,7 +8289,7 @@
         <v>72</v>
       </c>
       <c r="F140" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G140" t="s">
         <v>88</v>
@@ -8293,7 +8298,7 @@
         <v>75</v>
       </c>
       <c r="I140" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J140" s="2">
         <v>46080</v>
@@ -8324,7 +8329,7 @@
         <v>72</v>
       </c>
       <c r="F141" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G141" t="s">
         <v>88</v>
@@ -8333,7 +8338,7 @@
         <v>75</v>
       </c>
       <c r="I141" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J141" s="2">
         <v>46080</v>
@@ -8371,7 +8376,7 @@
         <v>72</v>
       </c>
       <c r="F142" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G142" t="s">
         <v>75</v>
@@ -8380,7 +8385,7 @@
         <v>100</v>
       </c>
       <c r="I142" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J142" s="2">
         <v>46081</v>
@@ -8418,7 +8423,7 @@
         <v>72</v>
       </c>
       <c r="F143" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G143" t="s">
         <v>88</v>
@@ -8427,7 +8432,7 @@
         <v>75</v>
       </c>
       <c r="I143" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J143" s="2">
         <v>46080</v>
@@ -8458,7 +8463,7 @@
         <v>72</v>
       </c>
       <c r="F144" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G144" t="s">
         <v>88</v>
@@ -8467,7 +8472,7 @@
         <v>75</v>
       </c>
       <c r="I144" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J144" s="2">
         <v>46080</v>
@@ -8502,7 +8507,7 @@
         <v>71</v>
       </c>
       <c r="F145" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G145" t="s">
         <v>75</v>
@@ -8511,7 +8516,7 @@
         <v>118</v>
       </c>
       <c r="I145" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J145" s="2">
         <v>46081</v>
@@ -8549,7 +8554,7 @@
         <v>72</v>
       </c>
       <c r="F146" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G146" t="s">
         <v>119</v>
@@ -8558,7 +8563,7 @@
         <v>119</v>
       </c>
       <c r="I146" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J146" s="2">
         <v>46066</v>
@@ -8589,7 +8594,7 @@
         <v>72</v>
       </c>
       <c r="F147" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G147" t="s">
         <v>119</v>
@@ -8598,7 +8603,7 @@
         <v>119</v>
       </c>
       <c r="I147" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J147" s="2">
         <v>46066</v>
@@ -8636,7 +8641,7 @@
         <v>72</v>
       </c>
       <c r="F148" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G148" t="s">
         <v>119</v>
@@ -8645,7 +8650,7 @@
         <v>119</v>
       </c>
       <c r="I148" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J148" s="2">
         <v>46066</v>
@@ -8680,7 +8685,7 @@
         <v>71</v>
       </c>
       <c r="F149" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G149" t="s">
         <v>119</v>
@@ -8689,7 +8694,7 @@
         <v>120</v>
       </c>
       <c r="I149" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J149" s="2">
         <v>46067</v>
@@ -8727,7 +8732,7 @@
         <v>72</v>
       </c>
       <c r="F150" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G150" t="s">
         <v>102</v>
@@ -8736,7 +8741,7 @@
         <v>74</v>
       </c>
       <c r="I150" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J150" s="2">
         <v>46068</v>
@@ -8767,7 +8772,7 @@
         <v>72</v>
       </c>
       <c r="F151" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G151" t="s">
         <v>102</v>
@@ -8776,7 +8781,7 @@
         <v>74</v>
       </c>
       <c r="I151" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J151" s="2">
         <v>46068</v>
@@ -8811,7 +8816,7 @@
         <v>71</v>
       </c>
       <c r="F152" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G152" t="s">
         <v>74</v>
@@ -8820,7 +8825,7 @@
         <v>77</v>
       </c>
       <c r="I152" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J152" s="2">
         <v>46069</v>
@@ -8858,7 +8863,7 @@
         <v>72</v>
       </c>
       <c r="F153" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G153" t="s">
         <v>121</v>
@@ -8867,7 +8872,7 @@
         <v>74</v>
       </c>
       <c r="I153" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J153" s="2">
         <v>46083</v>
@@ -8898,7 +8903,7 @@
         <v>72</v>
       </c>
       <c r="F154" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G154" t="s">
         <v>121</v>
@@ -8907,7 +8912,7 @@
         <v>74</v>
       </c>
       <c r="I154" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J154" s="2">
         <v>46083</v>
@@ -8942,7 +8947,7 @@
         <v>71</v>
       </c>
       <c r="F155" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G155" t="s">
         <v>74</v>
@@ -8951,7 +8956,7 @@
         <v>90</v>
       </c>
       <c r="I155" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J155" s="2">
         <v>46084</v>
@@ -8989,7 +8994,7 @@
         <v>98</v>
       </c>
       <c r="F156" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G156" t="s">
         <v>122</v>
@@ -8998,7 +9003,7 @@
         <v>74</v>
       </c>
       <c r="I156" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J156" s="2">
         <v>46074</v>
@@ -9026,7 +9031,7 @@
         <v>71</v>
       </c>
       <c r="F157" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G157" t="s">
         <v>74</v>
@@ -9035,7 +9040,7 @@
         <v>123</v>
       </c>
       <c r="I157" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J157" s="2">
         <v>46075</v>
@@ -9073,7 +9078,7 @@
         <v>72</v>
       </c>
       <c r="F158" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G158" t="s">
         <v>124</v>
@@ -9082,7 +9087,7 @@
         <v>108</v>
       </c>
       <c r="I158" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J158" s="2">
         <v>46075</v>
@@ -9113,7 +9118,7 @@
         <v>72</v>
       </c>
       <c r="F159" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G159" t="s">
         <v>124</v>
@@ -9122,7 +9127,7 @@
         <v>108</v>
       </c>
       <c r="I159" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J159" s="2">
         <v>46075</v>
@@ -9160,7 +9165,7 @@
         <v>98</v>
       </c>
       <c r="F160" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G160" t="s">
         <v>108</v>
@@ -9169,7 +9174,7 @@
         <v>125</v>
       </c>
       <c r="I160" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J160" s="2">
         <v>46076</v>
@@ -9207,7 +9212,7 @@
         <v>72</v>
       </c>
       <c r="F161" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G161" t="s">
         <v>124</v>
@@ -9216,7 +9221,7 @@
         <v>108</v>
       </c>
       <c r="I161" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J161" s="2">
         <v>46075</v>
@@ -9247,7 +9252,7 @@
         <v>98</v>
       </c>
       <c r="F162" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G162" t="s">
         <v>108</v>
@@ -9256,7 +9261,7 @@
         <v>125</v>
       </c>
       <c r="I162" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J162" s="2">
         <v>46076</v>
@@ -9294,7 +9299,7 @@
         <v>98</v>
       </c>
       <c r="F163" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G163" t="s">
         <v>124</v>
@@ -9303,7 +9308,7 @@
         <v>126</v>
       </c>
       <c r="I163" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J163" s="2">
         <v>46075</v>
@@ -9334,7 +9339,7 @@
         <v>98</v>
       </c>
       <c r="F164" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G164" t="s">
         <v>124</v>
@@ -9343,7 +9348,7 @@
         <v>126</v>
       </c>
       <c r="I164" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J164" s="2">
         <v>46075</v>
@@ -9381,7 +9386,7 @@
         <v>98</v>
       </c>
       <c r="F165" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G165" t="s">
         <v>126</v>
@@ -9390,7 +9395,7 @@
         <v>125</v>
       </c>
       <c r="I165" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J165" s="2">
         <v>46076</v>
@@ -9428,7 +9433,7 @@
         <v>98</v>
       </c>
       <c r="F166" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G166" t="s">
         <v>124</v>
@@ -9437,7 +9442,7 @@
         <v>108</v>
       </c>
       <c r="I166" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J166" s="2">
         <v>46075</v>
@@ -9468,7 +9473,7 @@
         <v>98</v>
       </c>
       <c r="F167" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G167" t="s">
         <v>124</v>
@@ -9477,7 +9482,7 @@
         <v>108</v>
       </c>
       <c r="I167" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J167" s="2">
         <v>46075</v>
@@ -9515,7 +9520,7 @@
         <v>98</v>
       </c>
       <c r="F168" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G168" t="s">
         <v>108</v>
@@ -9524,7 +9529,7 @@
         <v>125</v>
       </c>
       <c r="I168" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J168" s="2">
         <v>46076</v>
@@ -9562,7 +9567,7 @@
         <v>72</v>
       </c>
       <c r="F169" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G169" t="s">
         <v>124</v>
@@ -9571,7 +9576,7 @@
         <v>108</v>
       </c>
       <c r="I169" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J169" s="2">
         <v>46075</v>
@@ -9602,7 +9607,7 @@
         <v>98</v>
       </c>
       <c r="F170" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G170" t="s">
         <v>108</v>
@@ -9611,7 +9616,7 @@
         <v>125</v>
       </c>
       <c r="I170" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J170" s="2">
         <v>46076</v>
@@ -9649,7 +9654,7 @@
         <v>72</v>
       </c>
       <c r="F171" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G171" t="s">
         <v>108</v>
@@ -9658,7 +9663,7 @@
         <v>108</v>
       </c>
       <c r="I171" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J171" s="2">
         <v>46094</v>
@@ -9689,7 +9694,7 @@
         <v>72</v>
       </c>
       <c r="F172" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G172" t="s">
         <v>108</v>
@@ -9698,7 +9703,7 @@
         <v>127</v>
       </c>
       <c r="I172" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J172" s="2">
         <v>46095</v>
@@ -9736,7 +9741,7 @@
         <v>72</v>
       </c>
       <c r="F173" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G173" t="s">
         <v>78</v>
@@ -9745,7 +9750,7 @@
         <v>79</v>
       </c>
       <c r="I173" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J173" s="2">
         <v>46094</v>
@@ -9776,7 +9781,7 @@
         <v>72</v>
       </c>
       <c r="F174" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G174" t="s">
         <v>78</v>
@@ -9785,7 +9790,7 @@
         <v>79</v>
       </c>
       <c r="I174" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J174" s="2">
         <v>46094</v>
@@ -9823,7 +9828,7 @@
         <v>72</v>
       </c>
       <c r="F175" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G175" t="s">
         <v>79</v>
@@ -9832,7 +9837,7 @@
         <v>128</v>
       </c>
       <c r="I175" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J175" s="2">
         <v>46095</v>
@@ -9867,7 +9872,7 @@
         <v>71</v>
       </c>
       <c r="F176" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G176" t="s">
         <v>128</v>
@@ -9876,7 +9881,7 @@
         <v>107</v>
       </c>
       <c r="I176" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J176" s="2">
         <v>46095</v>
@@ -9914,7 +9919,7 @@
         <v>72</v>
       </c>
       <c r="F177" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G177" t="s">
         <v>78</v>
@@ -9923,7 +9928,7 @@
         <v>79</v>
       </c>
       <c r="I177" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J177" s="2">
         <v>46094</v>
@@ -9954,7 +9959,7 @@
         <v>72</v>
       </c>
       <c r="F178" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G178" t="s">
         <v>79</v>
@@ -9963,7 +9968,7 @@
         <v>128</v>
       </c>
       <c r="I178" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J178" s="2">
         <v>46095</v>
@@ -9998,7 +10003,7 @@
         <v>71</v>
       </c>
       <c r="F179" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G179" t="s">
         <v>128</v>
@@ -10007,7 +10012,7 @@
         <v>129</v>
       </c>
       <c r="I179" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J179" s="2">
         <v>46095</v>
@@ -10045,7 +10050,7 @@
         <v>72</v>
       </c>
       <c r="F180" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G180" t="s">
         <v>78</v>
@@ -10054,7 +10059,7 @@
         <v>79</v>
       </c>
       <c r="I180" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J180" s="2">
         <v>46094</v>
@@ -10085,7 +10090,7 @@
         <v>72</v>
       </c>
       <c r="F181" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G181" t="s">
         <v>79</v>
@@ -10094,7 +10099,7 @@
         <v>128</v>
       </c>
       <c r="I181" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J181" s="2">
         <v>46095</v>
@@ -10129,7 +10134,7 @@
         <v>71</v>
       </c>
       <c r="F182" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G182" t="s">
         <v>128</v>
@@ -10138,7 +10143,7 @@
         <v>129</v>
       </c>
       <c r="I182" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J182" s="2">
         <v>46095</v>
@@ -10173,7 +10178,7 @@
         <v>81</v>
       </c>
       <c r="F183" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G183" t="s">
         <v>104</v>
@@ -10182,7 +10187,7 @@
         <v>130</v>
       </c>
       <c r="I183" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J183" s="2">
         <v>46094</v>
@@ -10210,7 +10215,7 @@
         <v>81</v>
       </c>
       <c r="F184" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G184" t="s">
         <v>130</v>
@@ -10219,7 +10224,7 @@
         <v>131</v>
       </c>
       <c r="I184" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J184" s="2">
         <v>46094</v>
@@ -10254,13 +10259,13 @@
         <v>81</v>
       </c>
       <c r="F185" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G185" t="s">
         <v>130</v>
       </c>
       <c r="I185" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J185" s="2">
         <v>46094</v>
@@ -10298,7 +10303,7 @@
         <v>72</v>
       </c>
       <c r="F186" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G186" t="s">
         <v>131</v>
@@ -10307,7 +10312,7 @@
         <v>130</v>
       </c>
       <c r="I186" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J186" s="2">
         <v>46095</v>
@@ -10345,7 +10350,7 @@
         <v>72</v>
       </c>
       <c r="F187" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G187" t="s">
         <v>109</v>
@@ -10354,7 +10359,7 @@
         <v>109</v>
       </c>
       <c r="I187" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J187" s="2">
         <v>46095</v>
@@ -10382,7 +10387,7 @@
         <v>71</v>
       </c>
       <c r="F188" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G188" t="s">
         <v>109</v>
@@ -10391,7 +10396,7 @@
         <v>100</v>
       </c>
       <c r="I188" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J188" s="2">
         <v>46096</v>
@@ -10429,7 +10434,7 @@
         <v>72</v>
       </c>
       <c r="F189" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G189" t="s">
         <v>109</v>
@@ -10438,7 +10443,7 @@
         <v>109</v>
       </c>
       <c r="I189" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J189" s="2">
         <v>46095</v>
@@ -10466,7 +10471,7 @@
         <v>71</v>
       </c>
       <c r="F190" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G190" t="s">
         <v>109</v>
@@ -10475,7 +10480,7 @@
         <v>107</v>
       </c>
       <c r="I190" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J190" s="2">
         <v>46096</v>
@@ -10513,7 +10518,7 @@
         <v>72</v>
       </c>
       <c r="F191" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G191" t="s">
         <v>108</v>
@@ -10522,7 +10527,7 @@
         <v>126</v>
       </c>
       <c r="I191" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J191" s="2">
         <v>46082</v>
@@ -10553,7 +10558,7 @@
         <v>72</v>
       </c>
       <c r="F192" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G192" t="s">
         <v>113</v>
@@ -10562,7 +10567,7 @@
         <v>108</v>
       </c>
       <c r="I192" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J192" s="2">
         <v>46082</v>
@@ -10600,7 +10605,7 @@
         <v>72</v>
       </c>
       <c r="F193" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G193" t="s">
         <v>113</v>
@@ -10609,7 +10614,7 @@
         <v>108</v>
       </c>
       <c r="I193" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J193" s="2">
         <v>46082</v>
@@ -10644,7 +10649,7 @@
         <v>71</v>
       </c>
       <c r="F194" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G194" t="s">
         <v>126</v>
@@ -10653,7 +10658,7 @@
         <v>132</v>
       </c>
       <c r="I194" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J194" s="2">
         <v>46083</v>
@@ -10691,7 +10696,7 @@
         <v>98</v>
       </c>
       <c r="F195" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G195" t="s">
         <v>133</v>
@@ -10700,7 +10705,7 @@
         <v>75</v>
       </c>
       <c r="I195" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J195" s="2">
         <v>46088</v>
@@ -10728,7 +10733,7 @@
         <v>71</v>
       </c>
       <c r="F196" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G196" t="s">
         <v>75</v>
@@ -10737,7 +10742,7 @@
         <v>111</v>
       </c>
       <c r="I196" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J196" s="2">
         <v>46089</v>
@@ -10775,7 +10780,7 @@
         <v>98</v>
       </c>
       <c r="F197" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G197" t="s">
         <v>133</v>
@@ -10784,7 +10789,7 @@
         <v>75</v>
       </c>
       <c r="I197" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J197" s="2">
         <v>46088</v>
@@ -10812,7 +10817,7 @@
         <v>71</v>
       </c>
       <c r="F198" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G198" t="s">
         <v>75</v>
@@ -10821,7 +10826,7 @@
         <v>90</v>
       </c>
       <c r="I198" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J198" s="2">
         <v>46089</v>
@@ -10859,7 +10864,7 @@
         <v>72</v>
       </c>
       <c r="F199" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G199" t="s">
         <v>134</v>
@@ -10868,7 +10873,7 @@
         <v>103</v>
       </c>
       <c r="I199" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J199" s="2">
         <v>46090</v>
@@ -10899,7 +10904,7 @@
         <v>72</v>
       </c>
       <c r="F200" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G200" t="s">
         <v>134</v>
@@ -10908,7 +10913,7 @@
         <v>103</v>
       </c>
       <c r="I200" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J200" s="2">
         <v>46090</v>
@@ -10943,7 +10948,7 @@
         <v>71</v>
       </c>
       <c r="F201" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G201" t="s">
         <v>103</v>
@@ -10952,7 +10957,7 @@
         <v>135</v>
       </c>
       <c r="I201" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J201" s="2">
         <v>46091</v>
@@ -10990,7 +10995,7 @@
         <v>72</v>
       </c>
       <c r="F202" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G202" t="s">
         <v>119</v>
@@ -10999,7 +11004,7 @@
         <v>86</v>
       </c>
       <c r="I202" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J202" s="2">
         <v>46104</v>
@@ -11030,7 +11035,7 @@
         <v>72</v>
       </c>
       <c r="F203" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G203" t="s">
         <v>119</v>
@@ -11039,7 +11044,7 @@
         <v>86</v>
       </c>
       <c r="I203" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J203" s="2">
         <v>46104</v>
@@ -11074,7 +11079,7 @@
         <v>71</v>
       </c>
       <c r="F204" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G204" t="s">
         <v>86</v>
@@ -11083,7 +11088,7 @@
         <v>89</v>
       </c>
       <c r="I204" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J204" s="2">
         <v>46105</v>
@@ -11121,7 +11126,7 @@
         <v>72</v>
       </c>
       <c r="F205" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G205" t="s">
         <v>119</v>
@@ -11130,7 +11135,7 @@
         <v>86</v>
       </c>
       <c r="I205" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J205" s="2">
         <v>46104</v>
@@ -11161,7 +11166,7 @@
         <v>72</v>
       </c>
       <c r="F206" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G206" t="s">
         <v>119</v>
@@ -11170,7 +11175,7 @@
         <v>86</v>
       </c>
       <c r="I206" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J206" s="2">
         <v>46104</v>
@@ -11205,7 +11210,7 @@
         <v>71</v>
       </c>
       <c r="F207" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G207" t="s">
         <v>86</v>
@@ -11214,7 +11219,7 @@
         <v>100</v>
       </c>
       <c r="I207" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J207" s="2">
         <v>46105</v>
@@ -11252,7 +11257,7 @@
         <v>72</v>
       </c>
       <c r="F208" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G208" t="s">
         <v>119</v>
@@ -11261,7 +11266,7 @@
         <v>86</v>
       </c>
       <c r="I208" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J208" s="2">
         <v>46104</v>
@@ -11292,7 +11297,7 @@
         <v>72</v>
       </c>
       <c r="F209" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G209" t="s">
         <v>119</v>
@@ -11301,7 +11306,7 @@
         <v>86</v>
       </c>
       <c r="I209" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J209" s="2">
         <v>46104</v>
@@ -11336,7 +11341,7 @@
         <v>71</v>
       </c>
       <c r="F210" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G210" t="s">
         <v>86</v>
@@ -11345,7 +11350,7 @@
         <v>90</v>
       </c>
       <c r="I210" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J210" s="2">
         <v>46105</v>
@@ -11383,7 +11388,7 @@
         <v>72</v>
       </c>
       <c r="F211" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G211" t="s">
         <v>136</v>
@@ -11392,7 +11397,7 @@
         <v>77</v>
       </c>
       <c r="I211" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J211" s="2">
         <v>46106</v>
@@ -11420,7 +11425,7 @@
         <v>71</v>
       </c>
       <c r="F212" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G212" t="s">
         <v>77</v>
@@ -11429,7 +11434,7 @@
         <v>123</v>
       </c>
       <c r="I212" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J212" s="2">
         <v>46107</v>
@@ -11467,7 +11472,7 @@
         <v>72</v>
       </c>
       <c r="F213" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G213" t="s">
         <v>136</v>
@@ -11476,7 +11481,7 @@
         <v>77</v>
       </c>
       <c r="I213" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J213" s="2">
         <v>46106</v>
@@ -11504,7 +11509,7 @@
         <v>71</v>
       </c>
       <c r="F214" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G214" t="s">
         <v>77</v>
@@ -11513,7 +11518,7 @@
         <v>90</v>
       </c>
       <c r="I214" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J214" s="2">
         <v>46107</v>
@@ -11548,7 +11553,7 @@
         <v>71</v>
       </c>
       <c r="F215" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G215" t="s">
         <v>136</v>
@@ -11557,7 +11562,7 @@
         <v>74</v>
       </c>
       <c r="I215" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J215" s="2">
         <v>46106</v>
@@ -11585,7 +11590,7 @@
         <v>71</v>
       </c>
       <c r="F216" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G216" t="s">
         <v>74</v>
@@ -11594,7 +11599,7 @@
         <v>123</v>
       </c>
       <c r="I216" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J216" s="2">
         <v>46107</v>
@@ -11632,7 +11637,7 @@
         <v>72</v>
       </c>
       <c r="F217" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G217" t="s">
         <v>136</v>
@@ -11641,7 +11646,7 @@
         <v>74</v>
       </c>
       <c r="I217" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J217" s="2">
         <v>46106</v>
@@ -11672,7 +11677,7 @@
         <v>72</v>
       </c>
       <c r="F218" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G218" t="s">
         <v>136</v>
@@ -11681,7 +11686,7 @@
         <v>74</v>
       </c>
       <c r="I218" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J218" s="2">
         <v>46106</v>
@@ -11716,7 +11721,7 @@
         <v>71</v>
       </c>
       <c r="F219" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G219" t="s">
         <v>74</v>
@@ -11725,7 +11730,7 @@
         <v>123</v>
       </c>
       <c r="I219" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J219" s="2">
         <v>46107</v>
@@ -11763,7 +11768,7 @@
         <v>72</v>
       </c>
       <c r="F220" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G220" t="s">
         <v>136</v>
@@ -11772,7 +11777,7 @@
         <v>74</v>
       </c>
       <c r="I220" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J220" s="2">
         <v>46106</v>
@@ -11803,7 +11808,7 @@
         <v>72</v>
       </c>
       <c r="F221" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G221" t="s">
         <v>136</v>
@@ -11812,7 +11817,7 @@
         <v>74</v>
       </c>
       <c r="I221" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J221" s="2">
         <v>46106</v>
@@ -11847,7 +11852,7 @@
         <v>71</v>
       </c>
       <c r="F222" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G222" t="s">
         <v>74</v>
@@ -11856,7 +11861,7 @@
         <v>116</v>
       </c>
       <c r="I222" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J222" s="2">
         <v>46107</v>
@@ -11894,7 +11899,7 @@
         <v>72</v>
       </c>
       <c r="F223" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G223" t="s">
         <v>109</v>
@@ -11903,7 +11908,7 @@
         <v>109</v>
       </c>
       <c r="I223" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J223" s="2">
         <v>46108</v>
@@ -11931,7 +11936,7 @@
         <v>71</v>
       </c>
       <c r="F224" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G224" t="s">
         <v>109</v>
@@ -11940,7 +11945,7 @@
         <v>100</v>
       </c>
       <c r="I224" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J224" s="2">
         <v>46109</v>
@@ -11978,7 +11983,7 @@
         <v>72</v>
       </c>
       <c r="F225" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G225" t="s">
         <v>109</v>
@@ -11987,7 +11992,7 @@
         <v>74</v>
       </c>
       <c r="I225" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J225" s="2">
         <v>46108</v>
@@ -12015,7 +12020,7 @@
         <v>71</v>
       </c>
       <c r="F226" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G226" t="s">
         <v>74</v>
@@ -12024,7 +12029,7 @@
         <v>107</v>
       </c>
       <c r="I226" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J226" s="2">
         <v>46109</v>
@@ -12062,7 +12067,7 @@
         <v>72</v>
       </c>
       <c r="F227" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G227" t="s">
         <v>109</v>
@@ -12071,7 +12076,7 @@
         <v>109</v>
       </c>
       <c r="I227" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J227" s="2">
         <v>46095</v>
@@ -12099,7 +12104,7 @@
         <v>71</v>
       </c>
       <c r="F228" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G228" t="s">
         <v>109</v>
@@ -12108,7 +12113,7 @@
         <v>118</v>
       </c>
       <c r="I228" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J228" s="2">
         <v>46096</v>
@@ -12143,7 +12148,7 @@
         <v>81</v>
       </c>
       <c r="F229" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G229" t="s">
         <v>137</v>
@@ -12152,7 +12157,7 @@
         <v>131</v>
       </c>
       <c r="I229" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J229" s="2">
         <v>46094</v>
@@ -12183,7 +12188,7 @@
         <v>72</v>
       </c>
       <c r="F230" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G230" t="s">
         <v>131</v>
@@ -12192,7 +12197,7 @@
         <v>130</v>
       </c>
       <c r="I230" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J230" s="2">
         <v>46095</v>
@@ -12230,7 +12235,7 @@
         <v>72</v>
       </c>
       <c r="F231" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G231" t="s">
         <v>78</v>
@@ -12239,7 +12244,7 @@
         <v>79</v>
       </c>
       <c r="I231" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J231" s="2">
         <v>46094</v>
@@ -12270,7 +12275,7 @@
         <v>72</v>
       </c>
       <c r="F232" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G232" t="s">
         <v>79</v>
@@ -12279,7 +12284,7 @@
         <v>128</v>
       </c>
       <c r="I232" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J232" s="2">
         <v>46095</v>
@@ -12314,7 +12319,7 @@
         <v>71</v>
       </c>
       <c r="F233" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G233" t="s">
         <v>128</v>
@@ -12323,7 +12328,7 @@
         <v>107</v>
       </c>
       <c r="I233" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J233" s="2">
         <v>46095</v>
@@ -12361,7 +12366,7 @@
         <v>72</v>
       </c>
       <c r="F234" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G234" t="s">
         <v>113</v>
@@ -12370,7 +12375,7 @@
         <v>113</v>
       </c>
       <c r="I234" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J234" s="2">
         <v>46110</v>
@@ -12401,7 +12406,7 @@
         <v>72</v>
       </c>
       <c r="F235" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G235" t="s">
         <v>113</v>
@@ -12410,7 +12415,7 @@
         <v>113</v>
       </c>
       <c r="I235" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J235" s="2">
         <v>46110</v>
@@ -12448,7 +12453,7 @@
         <v>72</v>
       </c>
       <c r="F236" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G236" t="s">
         <v>113</v>
@@ -12457,7 +12462,7 @@
         <v>113</v>
       </c>
       <c r="I236" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J236" s="2">
         <v>46110</v>
@@ -12492,7 +12497,7 @@
         <v>71</v>
       </c>
       <c r="F237" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G237" t="s">
         <v>113</v>
@@ -12501,7 +12506,7 @@
         <v>95</v>
       </c>
       <c r="I237" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J237" s="2">
         <v>46111</v>
@@ -12539,7 +12544,7 @@
         <v>72</v>
       </c>
       <c r="F238" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G238" t="s">
         <v>138</v>
@@ -12548,7 +12553,7 @@
         <v>86</v>
       </c>
       <c r="I238" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J238" s="2">
         <v>46110</v>
@@ -12579,7 +12584,7 @@
         <v>72</v>
       </c>
       <c r="F239" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G239" t="s">
         <v>138</v>
@@ -12588,7 +12593,7 @@
         <v>86</v>
       </c>
       <c r="I239" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J239" s="2">
         <v>46110</v>
@@ -12623,7 +12628,7 @@
         <v>71</v>
       </c>
       <c r="F240" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G240" t="s">
         <v>86</v>
@@ -12632,7 +12637,7 @@
         <v>90</v>
       </c>
       <c r="I240" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J240" s="2">
         <v>46111</v>
@@ -12670,7 +12675,7 @@
         <v>72</v>
       </c>
       <c r="F241" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G241" t="s">
         <v>119</v>
@@ -12679,7 +12684,7 @@
         <v>86</v>
       </c>
       <c r="I241" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J241" s="2">
         <v>46104</v>
@@ -12707,7 +12712,7 @@
         <v>71</v>
       </c>
       <c r="F242" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G242" t="s">
         <v>86</v>
@@ -12716,7 +12721,7 @@
         <v>89</v>
       </c>
       <c r="I242" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J242" s="2">
         <v>46105</v>
@@ -12754,7 +12759,7 @@
         <v>72</v>
       </c>
       <c r="F243" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G243" t="s">
         <v>134</v>
@@ -12763,7 +12768,7 @@
         <v>74</v>
       </c>
       <c r="I243" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J243" s="2">
         <v>46111</v>
@@ -12794,7 +12799,7 @@
         <v>72</v>
       </c>
       <c r="F244" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G244" t="s">
         <v>134</v>
@@ -12803,7 +12808,7 @@
         <v>74</v>
       </c>
       <c r="I244" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J244" s="2">
         <v>46111</v>
@@ -12838,7 +12843,7 @@
         <v>71</v>
       </c>
       <c r="F245" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G245" t="s">
         <v>74</v>
@@ -12847,7 +12852,7 @@
         <v>90</v>
       </c>
       <c r="I245" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J245" s="2">
         <v>46112</v>
@@ -12885,7 +12890,7 @@
         <v>72</v>
       </c>
       <c r="F246" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G246" t="s">
         <v>136</v>
@@ -12894,7 +12899,7 @@
         <v>74</v>
       </c>
       <c r="I246" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J246" s="2">
         <v>46106</v>
@@ -12925,7 +12930,7 @@
         <v>72</v>
       </c>
       <c r="F247" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G247" t="s">
         <v>136</v>
@@ -12934,7 +12939,7 @@
         <v>74</v>
       </c>
       <c r="I247" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J247" s="2">
         <v>46106</v>
@@ -12969,7 +12974,7 @@
         <v>71</v>
       </c>
       <c r="F248" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G248" t="s">
         <v>74</v>
@@ -12978,7 +12983,7 @@
         <v>90</v>
       </c>
       <c r="I248" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J248" s="2">
         <v>46107</v>
@@ -13016,7 +13021,7 @@
         <v>72</v>
       </c>
       <c r="F249" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G249" t="s">
         <v>131</v>
@@ -13025,7 +13030,7 @@
         <v>74</v>
       </c>
       <c r="I249" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J249" s="2">
         <v>46102</v>
@@ -13056,7 +13061,7 @@
         <v>72</v>
       </c>
       <c r="F250" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G250" t="s">
         <v>131</v>
@@ -13065,7 +13070,7 @@
         <v>131</v>
       </c>
       <c r="I250" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J250" s="2">
         <v>46103</v>
@@ -13100,7 +13105,7 @@
         <v>71</v>
       </c>
       <c r="F251" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G251" t="s">
         <v>74</v>
@@ -13109,7 +13114,7 @@
         <v>90</v>
       </c>
       <c r="I251" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J251" s="2">
         <v>46103</v>
@@ -13147,7 +13152,7 @@
         <v>72</v>
       </c>
       <c r="F252" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G252" t="s">
         <v>131</v>
@@ -13156,7 +13161,7 @@
         <v>74</v>
       </c>
       <c r="I252" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J252" s="2">
         <v>46102</v>
@@ -13187,7 +13192,7 @@
         <v>72</v>
       </c>
       <c r="F253" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G253" t="s">
         <v>131</v>
@@ -13196,7 +13201,7 @@
         <v>131</v>
       </c>
       <c r="I253" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J253" s="2">
         <v>46103</v>
@@ -13234,7 +13239,7 @@
         <v>72</v>
       </c>
       <c r="F254" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G254" t="s">
         <v>131</v>
@@ -13243,7 +13248,7 @@
         <v>74</v>
       </c>
       <c r="I254" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J254" s="2">
         <v>46102</v>
@@ -13274,7 +13279,7 @@
         <v>72</v>
       </c>
       <c r="F255" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G255" t="s">
         <v>131</v>
@@ -13283,7 +13288,7 @@
         <v>131</v>
       </c>
       <c r="I255" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J255" s="2">
         <v>46103</v>
@@ -13321,7 +13326,7 @@
         <v>72</v>
       </c>
       <c r="F256" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G256" t="s">
         <v>131</v>
@@ -13330,7 +13335,7 @@
         <v>131</v>
       </c>
       <c r="I256" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J256" s="2">
         <v>46102</v>
@@ -13361,7 +13366,7 @@
         <v>72</v>
       </c>
       <c r="F257" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G257" t="s">
         <v>131</v>
@@ -13370,7 +13375,7 @@
         <v>74</v>
       </c>
       <c r="I257" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J257" s="2">
         <v>46103</v>
@@ -13408,7 +13413,7 @@
         <v>72</v>
       </c>
       <c r="F258" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G258" t="s">
         <v>131</v>
@@ -13417,7 +13422,7 @@
         <v>74</v>
       </c>
       <c r="I258" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J258" s="2">
         <v>46102</v>
@@ -13448,7 +13453,7 @@
         <v>72</v>
       </c>
       <c r="F259" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G259" t="s">
         <v>131</v>
@@ -13457,7 +13462,7 @@
         <v>131</v>
       </c>
       <c r="I259" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J259" s="2">
         <v>46103</v>
@@ -13492,7 +13497,7 @@
         <v>71</v>
       </c>
       <c r="F260" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G260" t="s">
         <v>74</v>
@@ -13501,7 +13506,7 @@
         <v>90</v>
       </c>
       <c r="I260" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J260" s="2">
         <v>46103</v>
@@ -13539,7 +13544,7 @@
         <v>72</v>
       </c>
       <c r="F261" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G261" t="s">
         <v>131</v>
@@ -13548,7 +13553,7 @@
         <v>74</v>
       </c>
       <c r="I261" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J261" s="2">
         <v>46102</v>
@@ -13579,7 +13584,7 @@
         <v>72</v>
       </c>
       <c r="F262" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G262" t="s">
         <v>131</v>
@@ -13588,7 +13593,7 @@
         <v>131</v>
       </c>
       <c r="I262" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J262" s="2">
         <v>46103</v>
@@ -13623,7 +13628,7 @@
         <v>71</v>
       </c>
       <c r="F263" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G263" t="s">
         <v>74</v>
@@ -13632,7 +13637,7 @@
         <v>89</v>
       </c>
       <c r="I263" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J263" s="2">
         <v>46103</v>
@@ -13670,7 +13675,7 @@
         <v>72</v>
       </c>
       <c r="F264" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G264" t="s">
         <v>131</v>
@@ -13679,7 +13684,7 @@
         <v>74</v>
       </c>
       <c r="I264" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J264" s="2">
         <v>46102</v>
@@ -13710,7 +13715,7 @@
         <v>72</v>
       </c>
       <c r="F265" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G265" t="s">
         <v>131</v>
@@ -13719,7 +13724,7 @@
         <v>131</v>
       </c>
       <c r="I265" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J265" s="2">
         <v>46103</v>
@@ -13757,7 +13762,7 @@
         <v>72</v>
       </c>
       <c r="F266" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G266" t="s">
         <v>131</v>
@@ -13766,7 +13771,7 @@
         <v>131</v>
       </c>
       <c r="I266" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J266" s="2">
         <v>46102</v>
@@ -13794,7 +13799,7 @@
         <v>71</v>
       </c>
       <c r="F267" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G267" t="s">
         <v>74</v>
@@ -13803,7 +13808,7 @@
         <v>89</v>
       </c>
       <c r="I267" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J267" s="2">
         <v>46103</v>
@@ -13841,7 +13846,7 @@
         <v>72</v>
       </c>
       <c r="F268" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G268" t="s">
         <v>131</v>
@@ -13850,7 +13855,7 @@
         <v>74</v>
       </c>
       <c r="I268" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J268" s="2">
         <v>46103</v>
@@ -13888,7 +13893,7 @@
         <v>72</v>
       </c>
       <c r="F269" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G269" t="s">
         <v>131</v>
@@ -13897,7 +13902,7 @@
         <v>74</v>
       </c>
       <c r="I269" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J269" s="2">
         <v>46102</v>
@@ -13928,7 +13933,7 @@
         <v>72</v>
       </c>
       <c r="F270" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G270" t="s">
         <v>131</v>
@@ -13937,7 +13942,7 @@
         <v>131</v>
       </c>
       <c r="I270" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J270" s="2">
         <v>46103</v>
@@ -13972,7 +13977,7 @@
         <v>71</v>
       </c>
       <c r="F271" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G271" t="s">
         <v>74</v>
@@ -13981,7 +13986,7 @@
         <v>90</v>
       </c>
       <c r="I271" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J271" s="2">
         <v>46103</v>
@@ -14019,7 +14024,7 @@
         <v>98</v>
       </c>
       <c r="F272" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G272" t="s">
         <v>99</v>
@@ -14028,7 +14033,7 @@
         <v>74</v>
       </c>
       <c r="I272" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J272" s="2">
         <v>46104</v>
@@ -14059,7 +14064,7 @@
         <v>98</v>
       </c>
       <c r="F273" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G273" t="s">
         <v>99</v>
@@ -14068,7 +14073,7 @@
         <v>74</v>
       </c>
       <c r="I273" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J273" s="2">
         <v>46104</v>
@@ -14103,7 +14108,7 @@
         <v>71</v>
       </c>
       <c r="F274" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G274" t="s">
         <v>74</v>
@@ -14112,7 +14117,7 @@
         <v>118</v>
       </c>
       <c r="I274" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J274" s="2">
         <v>46105</v>
@@ -14150,7 +14155,7 @@
         <v>72</v>
       </c>
       <c r="F275" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G275" t="s">
         <v>136</v>
@@ -14159,7 +14164,7 @@
         <v>77</v>
       </c>
       <c r="I275" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J275" s="2">
         <v>46106</v>
@@ -14187,7 +14192,7 @@
         <v>71</v>
       </c>
       <c r="F276" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G276" t="s">
         <v>77</v>
@@ -14196,7 +14201,7 @@
         <v>90</v>
       </c>
       <c r="I276" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J276" s="2">
         <v>46107</v>
@@ -14231,7 +14236,7 @@
         <v>71</v>
       </c>
       <c r="F277" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G277" t="s">
         <v>136</v>
@@ -14240,7 +14245,7 @@
         <v>74</v>
       </c>
       <c r="I277" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J277" s="2">
         <v>46106</v>
@@ -14268,7 +14273,7 @@
         <v>71</v>
       </c>
       <c r="F278" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G278" t="s">
         <v>74</v>
@@ -14277,7 +14282,7 @@
         <v>90</v>
       </c>
       <c r="I278" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J278" s="2">
         <v>46107</v>
@@ -14315,7 +14320,7 @@
         <v>72</v>
       </c>
       <c r="F279" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G279" t="s">
         <v>122</v>
@@ -14324,7 +14329,7 @@
         <v>94</v>
       </c>
       <c r="I279" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J279" s="2">
         <v>46109</v>
@@ -14352,13 +14357,13 @@
         <v>71</v>
       </c>
       <c r="F280" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G280" t="s">
         <v>94</v>
       </c>
       <c r="I280" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J280" s="2">
         <v>46110</v>
@@ -14396,7 +14401,7 @@
         <v>72</v>
       </c>
       <c r="F281" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G281" t="s">
         <v>122</v>
@@ -14405,7 +14410,7 @@
         <v>94</v>
       </c>
       <c r="I281" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J281" s="2">
         <v>46109</v>
@@ -14436,7 +14441,7 @@
         <v>72</v>
       </c>
       <c r="F282" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G282" t="s">
         <v>122</v>
@@ -14445,7 +14450,7 @@
         <v>94</v>
       </c>
       <c r="I282" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J282" s="2">
         <v>46109</v>
@@ -14480,13 +14485,13 @@
         <v>71</v>
       </c>
       <c r="F283" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G283" t="s">
         <v>94</v>
       </c>
       <c r="I283" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J283" s="2">
         <v>46110</v>
@@ -14524,7 +14529,7 @@
         <v>72</v>
       </c>
       <c r="F284" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G284" t="s">
         <v>138</v>
@@ -14533,7 +14538,7 @@
         <v>108</v>
       </c>
       <c r="I284" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J284" s="2">
         <v>46110</v>
@@ -14564,7 +14569,7 @@
         <v>72</v>
       </c>
       <c r="F285" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G285" t="s">
         <v>138</v>
@@ -14573,7 +14578,7 @@
         <v>108</v>
       </c>
       <c r="I285" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J285" s="2">
         <v>46110</v>
@@ -14608,7 +14613,7 @@
         <v>71</v>
       </c>
       <c r="F286" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G286" t="s">
         <v>108</v>
@@ -14617,7 +14622,7 @@
         <v>89</v>
       </c>
       <c r="I286" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J286" s="2">
         <v>46111</v>
@@ -14655,7 +14660,7 @@
         <v>72</v>
       </c>
       <c r="F287" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G287" t="s">
         <v>138</v>
@@ -14664,7 +14669,7 @@
         <v>108</v>
       </c>
       <c r="I287" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J287" s="2">
         <v>46110</v>
@@ -14695,7 +14700,7 @@
         <v>72</v>
       </c>
       <c r="F288" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G288" t="s">
         <v>138</v>
@@ -14704,7 +14709,7 @@
         <v>108</v>
       </c>
       <c r="I288" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J288" s="2">
         <v>46110</v>
@@ -14739,7 +14744,7 @@
         <v>71</v>
       </c>
       <c r="F289" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G289" t="s">
         <v>108</v>
@@ -14748,7 +14753,7 @@
         <v>90</v>
       </c>
       <c r="I289" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J289" s="2">
         <v>46111</v>
@@ -14786,7 +14791,7 @@
         <v>72</v>
       </c>
       <c r="F290" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G290" t="s">
         <v>138</v>
@@ -14795,7 +14800,7 @@
         <v>86</v>
       </c>
       <c r="I290" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J290" s="2">
         <v>46110</v>
@@ -14823,7 +14828,7 @@
         <v>71</v>
       </c>
       <c r="F291" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G291" t="s">
         <v>86</v>
@@ -14832,7 +14837,7 @@
         <v>100</v>
       </c>
       <c r="I291" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J291" s="2">
         <v>46111</v>
@@ -14880,7 +14885,7 @@
         <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G2" t="s">
         <v>64</v>
@@ -14889,13 +14894,13 @@
         <v>65</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
         <v>66</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
         <v>67</v>
